--- a/BlockchainLogisticsValidator/Data/Config.xlsx
+++ b/BlockchainLogisticsValidator/Data/Config.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -547,6 +547,7 @@
           <t>EtherscanApiKey</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Free key from etherscan.io/myapikey. Blank keeps API mode disabled.</t>
@@ -588,17 +589,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ExplorerAddressUrl</t>
+          <t>ExplorerPageUrl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://etherscan.io/address/{0}</t>
+          <t>Data\Input\MockChain\explorer_ethereum.html</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Used when DataSourceMode = WEB.</t>
+          <t>Used when DataSourceMode = WEB. A project-relative page, or a live explorer URL.</t>
         </is>
       </c>
     </row>
@@ -620,462 +621,483 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LogisticsFile</t>
+          <t>RunMode</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Data\Input\LogisticsRecords.xlsx</t>
+          <t>BATCH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ERP / WMS export.</t>
+          <t>BATCH validates the whole run in one job; DISPATCH splits it into one Orchestrator queue item per shipment.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ShipmentsSheet</t>
+          <t>QueueMode</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shipments</t>
+          <t>DRYRUN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Shipment master sheet name.</t>
+          <t>ORCHESTRATOR pushes real queue items; DRYRUN writes the payloads to disk for inspection.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ShipmentEventsSheet</t>
+          <t>QueueName</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ShipmentEvents</t>
+          <t>BlockchainValidationQueue</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Expected milestone lines.</t>
+          <t>Orchestrator queue used by Dispatcher and Performer.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TxShipmentMapFile</t>
+          <t>LogisticsFile</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Data\Input\TxShipmentMap.xlsx</t>
+          <t>Data\Input\LogisticsRecords.xlsx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Used when MappingMode = LOOKUP.</t>
+          <t>ERP / WMS export.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MappingMode</t>
+          <t>ShipmentsSheet</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DECODE</t>
+          <t>Shipments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DECODE reads the ABI input data; LOOKUP uses the mapping file.</t>
+          <t>Shipment master sheet name.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TimestampToleranceHours</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
+          <t>ShipmentEventsSheet</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ShipmentEvents</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>R1: drift up to this is a PASS.</t>
+          <t>Expected milestone lines.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TimestampWarnToleranceHours</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>4</v>
+          <t>TxShipmentMapFile</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Data\Input\TxShipmentMap.xlsx</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>R1: drift past this is a FAIL; between the two is a WARNING.</t>
+          <t>Used when MappingMode = LOOKUP.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QuantityTolerance</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
+          <t>MappingMode</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DECODE</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>R2: permitted absolute difference in units.</t>
+          <t>DECODE reads the ABI input data; LOOKUP uses the mapping file.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EscalationEnabled</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+          <t>TimestampToleranceHours</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Novelty 2: show the review form on a CRITICAL anomaly.</t>
+          <t>R1: drift up to this is a PASS.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EscalationSeverity</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
+          <t>TimestampWarnToleranceHours</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minimum severity that pauses the bot for a human.</t>
+          <t>R1: drift past this is a FAIL; between the two is a WARNING.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AttendedMode</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+          <t>QuantityTolerance</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>False in unattended runs: log and continue instead of blocking.</t>
+          <t>R2: permitted absolute difference in units.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AlertMode</t>
+          <t>EscalationEnabled</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EML</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EML writes the message to disk; SMTP and OUTLOOK actually send.</t>
+          <t>Novelty 2: show the review form on a CRITICAL anomaly.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AlertFrom</t>
+          <t>EscalationSeverity</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>rpa.bot@logistics-demo.local</t>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Minimum severity that pauses the bot for a human.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AlertTo</t>
+          <t>AttendedMode</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>logistics.manager@logistics-demo.local;compliance@logistics-demo.local</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Semicolon separated.</t>
+          <t>False in unattended runs: log and continue instead of blocking.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SmtpHost</t>
+          <t>EscalationMode</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>smtp.gmail.com</t>
+          <t>SIMULATE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Only used when AlertMode = SMTP.</t>
+          <t>PROMPT shows a reviewer dialog (attended only); SIMULATE applies the decision below; AUTO_LOG defers.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SmtpPort</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>587</v>
+          <t>SimulatedEscalationDecision</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>REJECTED - hold the shipment and open an investigation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Used when EscalationMode = SIMULATE, so rehearsals produce the same artefacts as a real review.</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SmtpUseSsl</t>
+          <t>AlertMode</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>EML</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EML writes the message to disk; SMTP and OUTLOOK actually send.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SmtpUser</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Leave blank unless AlertMode = SMTP.</t>
-        </is>
-      </c>
+          <t>AlertFrom</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>rpa.bot@logistics-demo.local</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SmtpPassword</t>
+          <t>AlertTo</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>logistics.manager@logistics-demo.local;compliance@logistics-demo.local</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>App password. Never commit a real value.</t>
+          <t>Semicolon separated.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ReportsFolder</t>
+          <t>SmtpHost</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Data\Output\Reports</t>
+          <t>smtp.gmail.com</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Only used when AlertMode = SMTP.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AuditLogFolder</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Data\Output\AuditLogs</t>
-        </is>
-      </c>
+          <t>SmtpPort</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>587</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AuditLogFile</t>
+          <t>SmtpUseSsl</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ValidationAuditLog.csv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Append-only, hash-chained.</t>
-        </is>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ScreenshotFolder</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Data\Output\Screenshots</t>
+          <t>SmtpUser</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Leave blank unless AlertMode = SMTP.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LogLevel</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Info</t>
-        </is>
-      </c>
+          <t>SmtpPassword</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Info | Trace.</t>
+          <t>App password. Never commit a real value.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EscalationMode</t>
+          <t>ReportsFolder</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SIMULATE</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>PROMPT shows a reviewer dialog (attended only); SIMULATE applies the decision below; AUTO_LOG defers.</t>
-        </is>
-      </c>
+          <t>Data\Output\Reports</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SimulatedEscalationDecision</t>
+          <t>AuditLogFolder</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>REJECTED - hold the shipment and open an investigation</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Used when EscalationMode = SIMULATE, so rehearsals produce the same artefacts as a real review.</t>
-        </is>
-      </c>
+          <t>Data\Output\AuditLogs</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QueueMode</t>
+          <t>AuditLogFile</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DRYRUN</t>
+          <t>ValidationAuditLog.csv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ORCHESTRATOR pushes real queue items; DRYRUN writes the payloads to disk for inspection.</t>
+          <t>Append-only, hash-chained.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QueueName</t>
+          <t>ScreenshotFolder</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BlockchainValidationQueue</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Orchestrator queue used by Dispatcher and Performer.</t>
-        </is>
-      </c>
+          <t>Data\Output\Screenshots</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RunMode</t>
+          <t>PdfReportEnabled</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BATCH</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BATCH validates the whole run in one job; DISPATCH splits it into one Orchestrator queue item per shipment.</t>
+          <t>Print the formal audit report to PDF with headless Edge.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ExplorerPageUrl</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Data\Input\MockChain\explorer_ethereum.html</t>
-        </is>
-      </c>
+          <t>PdfBrowserPath</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Used when DataSourceMode = WEB. A local replica by default; point at a live explorer URL and re-record the selector to scrape the real thing.</t>
+          <t>Blank finds Edge or Chrome automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LogLevel</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Info | Trace.</t>
         </is>
       </c>
     </row>
@@ -1207,6 +1229,7 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1239,6 +1262,8 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>ESCALATE</t>
@@ -1271,6 +1296,8 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1303,6 +1330,8 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1340,6 +1369,7 @@
           <t>GoodsReceived</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1605,6 +1635,7 @@
           <t>INTEGER</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1666,6 +1697,7 @@
           <t>LOWERCASE</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/BlockchainLogisticsValidator/Data/Config.xlsx
+++ b/BlockchainLogisticsValidator/Data/Config.xlsx
@@ -10,9 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ValidationRules" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ApprovedWallets" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldMapping" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventSequence" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventSignatures" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChainProfiles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldMapping" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventSequence" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventSignatures" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -750,93 +751,93 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DECODE reads the ABI input data; LOOKUP uses the mapping file.</t>
+          <t>DECODE takes shipment and milestone from the ABI call data; LOOKUP takes them from TxShipmentMap.xlsx.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TimestampToleranceHours</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2</v>
+          <t>ChainProfile</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ETHERSCAN</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>R1: drift up to this is a PASS.</t>
+          <t>Profile on the ChainProfiles sheet used for MOCK and API data. Onboarding a new chain = a new profile.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TimestampWarnToleranceHours</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>4</v>
+          <t>WebPageProfile</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EXPLORER_PAGE</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>R1: drift past this is a FAIL; between the two is a WARNING.</t>
+          <t>Profile used when DataSourceMode = WEB.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QuantityTolerance</t>
+          <t>TimestampToleranceHours</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>R2: permitted absolute difference in units.</t>
+          <t>R1: drift up to this is a PASS.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EscalationEnabled</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+          <t>TimestampWarnToleranceHours</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Novelty 2: show the review form on a CRITICAL anomaly.</t>
+          <t>R1: drift past this is a FAIL; between the two is a WARNING.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EscalationSeverity</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
+          <t>QuantityTolerance</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Minimum severity that pauses the bot for a human.</t>
+          <t>R2: permitted absolute difference in units.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AttendedMode</t>
+          <t>EscalationEnabled</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -846,210 +847,214 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>False in unattended runs: log and continue instead of blocking.</t>
+          <t>Novelty 2: show the review form on a CRITICAL anomaly.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EscalationMode</t>
+          <t>EscalationSeverity</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SIMULATE</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PROMPT shows a reviewer dialog (attended only); SIMULATE applies the decision below; AUTO_LOG defers.</t>
+          <t>Minimum severity that pauses the bot for a human.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SimulatedEscalationDecision</t>
+          <t>AttendedMode</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>REJECTED - hold the shipment and open an investigation</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Used when EscalationMode = SIMULATE, so rehearsals produce the same artefacts as a real review.</t>
+          <t>False in unattended runs: log and continue instead of blocking.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AlertMode</t>
+          <t>EscalationMode</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EML</t>
+          <t>SIMULATE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EML writes the message to disk; SMTP and OUTLOOK actually send.</t>
+          <t>PROMPT shows a reviewer dialog (attended only); SIMULATE applies the decision below; AUTO_LOG defers.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AlertFrom</t>
+          <t>SimulatedEscalationDecision</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>rpa.bot@logistics-demo.local</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>REJECTED - hold the shipment and open an investigation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Used when EscalationMode = SIMULATE, so rehearsals produce the same artefacts as a real review.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AlertTo</t>
+          <t>AlertMode</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>logistics.manager@logistics-demo.local;compliance@logistics-demo.local</t>
+          <t>EML</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Semicolon separated.</t>
+          <t>EML writes the message to disk; SMTP and OUTLOOK actually send.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SmtpHost</t>
+          <t>AlertFrom</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>smtp.gmail.com</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Only used when AlertMode = SMTP.</t>
-        </is>
-      </c>
+          <t>rpa.bot@logistics-demo.local</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SmtpPort</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>587</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>AlertTo</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>logistics.manager@logistics-demo.local;compliance@logistics-demo.local</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Semicolon separated.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SmtpUseSsl</t>
+          <t>SmtpHost</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>smtp.gmail.com</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Only used when AlertMode = SMTP.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SmtpUser</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Leave blank unless AlertMode = SMTP.</t>
-        </is>
-      </c>
+          <t>SmtpPort</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>587</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SmtpPassword</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>App password. Never commit a real value.</t>
-        </is>
-      </c>
+          <t>SmtpUseSsl</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ReportsFolder</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Data\Output\Reports</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>SmtpUser</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Leave blank unless AlertMode = SMTP.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AuditLogFolder</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Data\Output\AuditLogs</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>SmtpPassword</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>App password. Never commit a real value.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AuditLogFile</t>
+          <t>ReportsFolder</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ValidationAuditLog.csv</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Append-only, hash-chained.</t>
-        </is>
-      </c>
+          <t>Data\Output\Reports</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ScreenshotFolder</t>
+          <t>AuditLogFolder</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Data\Output\Screenshots</t>
+          <t>Data\Output\AuditLogs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1057,45 +1062,75 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PdfReportEnabled</t>
+          <t>AuditLogFile</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>ValidationAuditLog.csv</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Print the formal audit report to PDF with headless Edge.</t>
+          <t>Append-only, hash-chained.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PdfBrowserPath</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Blank finds Edge or Chrome automatically.</t>
-        </is>
-      </c>
+          <t>ScreenshotFolder</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Data\Output\Screenshots</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>PdfReportEnabled</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Print the formal audit report to PDF with headless Edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PdfBrowserPath</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Blank finds Edge or Chrome automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>LogLevel</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Info | Trace.</t>
         </is>
@@ -1566,246 +1601,105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="92" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BlockchainField</t>
+          <t>Profile</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>LogisticsField</t>
+          <t>RecordsPath</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>TransformType</t>
+          <t>StatusField</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>StatusOkValue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hash</t>
+          <t>ETHERSCAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TxHash</t>
+          <t>result</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LOWERCASE</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Transaction identity.</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Etherscan V2 account/txlist (also PolygonScan, BscScan). Flat records, epoch seconds.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>blockNumber</t>
+          <t>LEDGER_EXPORT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BlockNumber</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
+          <t>data.transactions</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Permissioned-ledger export. Nested JSON, ISO-8601 times, hex block numbers, no methodId field.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>timeStamp</t>
+          <t>EXPLORER_PAGE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EventTimestampUtc</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>EPOCH_TO_DATETIME</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Unix seconds to DateTime.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>from</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SenderAddress</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LOWERCASE</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Reconciles checksummed and non-checksummed forms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>to</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ContractAddress</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LOWERCASE</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>methodId</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>EventSelector</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LOWERCASE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Real keccak-256 function selector.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>input:arg0</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ShipmentID</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ABI_STRING</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>First ABI argument.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>input:arg1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>OnChainQty</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ABI_UINT256</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Second ABI argument.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>input:arg2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PONumber</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ABI_STRING</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Third ABI argument.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>isError</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TxFailed</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>BOOLEAN_INVERT</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Etherscan reports 0 for success.</t>
+          <t>records</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Rows scraped from an explorer's transaction table (01c wraps them as {records: [...]}).</t>
         </is>
       </c>
     </row>
@@ -1815,6 +1709,781 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>BlockchainField</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LogisticsField</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>TransformType</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ETHERSCAN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>hash</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TxHash</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Transaction identity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ETHERSCAN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>blockNumber</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BlockNumber</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ETHERSCAN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>timeStamp</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EventTimestampUtc</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EPOCH_TO_DATETIME</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Unix seconds to DateTime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ETHERSCAN</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SenderAddress</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Reconciles checksummed and non-checksummed forms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ETHERSCAN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ContractAddress</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ETHERSCAN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>methodId</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EventSelector</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Real keccak-256 function selector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ETHERSCAN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>input:arg0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ShipmentID</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ABI_STRING</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>First ABI argument.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ETHERSCAN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>input:arg1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OnChainQty</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ABI_UINT256</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Second ABI argument.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ETHERSCAN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>input:arg2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PONumber</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ABI_STRING</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Third ABI argument.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ETHERSCAN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>isError</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TxFailed</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Etherscan reports 1 for a reverted transaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LEDGER_EXPORT</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>txId</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TxHash</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Different field name for the same identity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LEDGER_EXPORT</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>block.number</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BlockNumber</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HEX_TO_INTEGER</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Nested, and hex-encoded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LEDGER_EXPORT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>confirmedAt</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EventTimestampUtc</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ISO_TO_DATETIME</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ISO-8601 rather than epoch seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LEDGER_EXPORT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>submitter</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SenderAddress</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LEDGER_EXPORT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ContractAddress</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LEDGER_EXPORT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EventSelector</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SELECTOR</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>No methodId field: derived from the first 4 bytes of the call data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LEDGER_EXPORT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>payload:arg0</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ShipmentID</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ABI_STRING</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LEDGER_EXPORT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>payload:arg1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OnChainQty</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ABI_UINT256</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LEDGER_EXPORT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>payload:arg2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PONumber</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ABI_STRING</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LEDGER_EXPORT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>reverted</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TxFailed</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>A JSON boolean rather than a 0/1 string.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EXPLORER_PAGE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TxHash</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TxHash</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Column headers of the scraped table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EXPLORER_PAGE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BlockNumber</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EXPLORER_PAGE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DateTimeUtc</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EventTimestampUtc</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ISO_TO_DATETIME</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Accepts 'yyyy-MM-dd HH:mm:ss' as well as ISO-8601.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EXPLORER_PAGE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SenderAddress</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EXPLORER_PAGE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ContractAddress</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>EXPLORER_PAGE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EventSelector</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SELECTOR</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EXPLORER_PAGE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Input:arg0</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ShipmentID</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ABI_STRING</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>EXPLORER_PAGE</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Input:arg1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>OnChainQty</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ABI_UINT256</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EXPLORER_PAGE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Input:arg2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PONumber</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ABI_STRING</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1962,7 +2631,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/BlockchainLogisticsValidator/Data/Config.xlsx
+++ b/BlockchainLogisticsValidator/Data/Config.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -932,159 +932,159 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EML writes the message to disk; SMTP and OUTLOOK actually send.</t>
+          <t>Delivery channels, comma-separated: EML (archive only), SMTP, WEBHOOK. The .eml copy is always written.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AlertFrom</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>rpa.bot@logistics-demo.local</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>AlertWebhookUrl</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Incoming-webhook URL for Teams, Slack or anything that accepts JSON.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AlertTo</t>
+          <t>AlertWebhookFormat</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>logistics.manager@logistics-demo.local;compliance@logistics-demo.local</t>
+          <t>TEAMS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Semicolon separated.</t>
+          <t>TEAMS (Adaptive Card) | SLACK (Block Kit) | GENERIC (plain JSON).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SmtpHost</t>
+          <t>AlertFrom</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>smtp.gmail.com</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Only used when AlertMode = SMTP.</t>
-        </is>
-      </c>
+          <t>rpa.bot@logistics-demo.local</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SmtpPort</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>587</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>AlertTo</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>logistics.manager@logistics-demo.local;compliance@logistics-demo.local</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Semicolon separated.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SmtpUseSsl</t>
+          <t>SmtpHost</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>smtp.gmail.com</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Only used when AlertMode = SMTP.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SmtpUser</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Leave blank unless AlertMode = SMTP.</t>
-        </is>
-      </c>
+          <t>SmtpPort</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>587</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SmtpPassword</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>App password. Never commit a real value.</t>
-        </is>
-      </c>
+          <t>SmtpUseSsl</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ReportsFolder</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Data\Output\Reports</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>SmtpUser</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Leave blank unless AlertMode = SMTP.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AuditLogFolder</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Data\Output\AuditLogs</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>SmtpPassword</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>App password. Never commit a real value.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AuditLogFile</t>
+          <t>ReportsFolder</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ValidationAuditLog.csv</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Append-only, hash-chained.</t>
-        </is>
-      </c>
+          <t>Data\Output\Reports</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ScreenshotFolder</t>
+          <t>AuditLogFolder</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Data\Output\Screenshots</t>
+          <t>Data\Output\AuditLogs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1092,45 +1092,75 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PdfReportEnabled</t>
+          <t>AuditLogFile</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>ValidationAuditLog.csv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Print the formal audit report to PDF with headless Edge.</t>
+          <t>Append-only, hash-chained.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PdfBrowserPath</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Blank finds Edge or Chrome automatically.</t>
-        </is>
-      </c>
+          <t>ScreenshotFolder</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Data\Output\Screenshots</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>PdfReportEnabled</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Print the formal audit report to PDF with headless Edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PdfBrowserPath</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Blank finds Edge or Chrome automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>LogLevel</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Info | Trace.</t>
         </is>

--- a/BlockchainLogisticsValidator/Data/Config.xlsx
+++ b/BlockchainLogisticsValidator/Data/Config.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ValidationRules" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ApprovedWallets" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldMapping" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventSequence" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventSignatures" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ValidationRules" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ApprovedWallets" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="FieldMapping" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FieldMapping_EvmEtl" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="EventSequence" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="EventSignatures" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -469,7 +470,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shown in reports and the audit log.</t>
+          <t>Shown in the Excel, PDF, e-mail and dashboard headers.</t>
         </is>
       </c>
     </row>
@@ -547,6 +548,7 @@
           <t>EtherscanApiKey</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Free key from etherscan.io/myapikey. Blank keeps API mode disabled.</t>
@@ -598,7 +600,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Used when DataSourceMode = WEB.</t>
+          <t>WEB mode: used when ExplorerPageUrl is blank; {0} becomes ContractAddress.</t>
         </is>
       </c>
     </row>
@@ -613,7 +615,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Upper bound per run.</t>
+          <t>Upper bound per run (API mode).</t>
         </is>
       </c>
     </row>
@@ -630,7 +632,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ERP / WMS export.</t>
+          <t>ERP / WMS export. Used when LogisticsSourceMode = EXCEL.</t>
         </is>
       </c>
     </row>
@@ -647,7 +649,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Shipment master sheet name.</t>
+          <t>Shipment master sheet name (EXCEL mode).</t>
         </is>
       </c>
     </row>
@@ -664,7 +666,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Expected milestone lines.</t>
+          <t>Expected milestone lines sheet name (EXCEL mode).</t>
         </is>
       </c>
     </row>
@@ -698,7 +700,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DECODE reads the ABI input data; LOOKUP uses the mapping file.</t>
+          <t>DECODE takes ShipmentID/PO from the ABI input data; LOOKUP takes them from TxShipmentMapFile by TxHash.</t>
         </is>
       </c>
     </row>
@@ -713,7 +715,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>R1: drift up to this is a PASS.</t>
+          <t>R1 fallback: used only when ValidationRules R1 Param1 is blank.</t>
         </is>
       </c>
     </row>
@@ -728,7 +730,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>R1: drift past this is a FAIL; between the two is a WARNING.</t>
+          <t>R1 fallback: used only when ValidationRules R1 Param2 is blank.</t>
         </is>
       </c>
     </row>
@@ -743,7 +745,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>R2: permitted absolute difference in units.</t>
+          <t>R2 fallback: used only when ValidationRules R2 Param1 is blank.</t>
         </is>
       </c>
     </row>
@@ -760,7 +762,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Novelty 2: show the review form on a CRITICAL anomaly.</t>
+          <t>Novelty 2: pause for a human reviewer on a high-severity anomaly.</t>
         </is>
       </c>
     </row>
@@ -777,7 +779,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minimum severity that pauses the bot for a human.</t>
+          <t>A FAIL at or above this severity escalates, as does any rule whose FailAction is ESCALATE. Blank = FailAction only.</t>
         </is>
       </c>
     </row>
@@ -811,7 +813,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EML writes the message to disk; SMTP and OUTLOOK actually send.</t>
+          <t>EML writes the message to disk; SMTP sends via SmtpHost; OUTLOOK sends via the desktop Outlook profile.</t>
         </is>
       </c>
     </row>
@@ -826,6 +828,11 @@
           <t>rpa.bot@logistics-demo.local</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sender address (EML and SMTP).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -870,6 +877,11 @@
       <c r="B27" t="n">
         <v>587</v>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>587 with SmtpUseSsl = True negotiates STARTTLS; 465 uses SSL on connect.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -882,6 +894,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>False connects without TLS (only for an internal relay).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -889,9 +906,10 @@
           <t>SmtpUser</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Leave blank unless AlertMode = SMTP.</t>
+          <t>Leave blank for an unauthenticated relay.</t>
         </is>
       </c>
     </row>
@@ -901,9 +919,10 @@
           <t>SmtpPassword</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>App password. Never commit a real value.</t>
+          <t>App password. Never commit a real value - use Config.local.json.</t>
         </is>
       </c>
     </row>
@@ -918,6 +937,11 @@
           <t>Data\Output\Reports</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Relative paths are resolved under the output root (BLV_OUTPUT_ROOT / Config.local.json).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -930,6 +954,11 @@
           <t>Data\Output\AuditLogs</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Relative paths are resolved under the output root.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -959,6 +988,11 @@
           <t>Data\Output\Screenshots</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Failure screenshots and reviewer-window evidence. Resolved under the output root.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -973,7 +1007,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Info | Trace.</t>
+          <t>Info | Trace. Trace also logs every transaction's verdict.</t>
         </is>
       </c>
     </row>
@@ -990,7 +1024,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PROMPT shows a reviewer dialog (attended only); SIMULATE applies the decision below; AUTO_LOG defers.</t>
+          <t>PROMPT shows the reviewer window (attended only); SIMULATE applies the decision below; AUTO_LOG defers.</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1109,325 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Used when DataSourceMode = WEB. A local replica by default; point at a live explorer URL and re-record the selector to scrape the real thing.</t>
+          <t>Used when DataSourceMode = WEB. A local replica by default; point at a live explorer URL to scrape the real thing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ChainRecordsPath</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>JSON path of the transaction array in a MOCK/API response. 'result' for Etherscan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FieldMappingSheet</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FieldMapping</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Which mapping sheet translates the feed's fields. FieldMapping = Etherscan; FieldMapping_EvmEtl = ethereum-etl export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>LogisticsSourceMode</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>EXCEL</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>EXCEL | CSV | SQL - where the ERP/WMS records are read from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ShipmentsCsvFile</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Data\Input\ERP_CSV\Shipments.csv</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Used when LogisticsSourceMode = CSV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ShipmentEventsCsvFile</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Data\Input\ERP_CSV\ShipmentEvents.csv</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Used when LogisticsSourceMode = CSV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DbProviderName</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>System.Data.Odbc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SQL mode: ADO.NET provider for Database Connect (System.Data.Odbc, System.Data.SqlClient, ...).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DbConnectionString</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Driver={Microsoft Access Driver (*.mdb, *.accdb)};Dbq={ProjectRoot}\Data\Input\LogisticsERP.accdb;</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SQL mode. {ProjectRoot} is replaced at run time. Put real credentials in Config.local.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DbShipmentsQuery</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SELECT * FROM Shipments ORDER BY ShipmentID</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SQL mode: must return the Shipments columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DbShipmentEventsQuery</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SELECT * FROM ShipmentEvents ORDER BY ShipmentID, ExpectedEventTimestampUtc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SQL mode: must return the ShipmentEvents columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ReviewUi</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>WINDOW</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PROMPT mode: WINDOW shows the full review form; DIALOG falls back to a simple Input Dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ReviewTimeoutMinutes</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>30</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>An unanswered review window closes after this long and the item is recorded as DEFERRED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AlertAttachReports</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Attach the Excel and PDF reports to SMTP / Outlook alerts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>OutlookAccount</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OUTLOOK mode: send from this account. Blank = the default profile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>OutlookSaveAsDraft</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>OUTLOOK mode: True saves the alert as a draft instead of sending it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TeamsWebhookUrl</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Teams Workflows webhook. Blank writes the Adaptive Card payload to Reports instead of posting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SlackWebhookUrl</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Slack incoming webhook. Blank writes the payload to Reports instead of posting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DashboardPushUrl</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Optional: Power BI streaming-dataset push URL or a Google Apps Script web app. Blank = no push.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DashboardPushFormat</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>POWERBI</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>POWERBI posts one flat KPI row; JSON posts the full dashboard_summary.json document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>RunHistoryFile</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>RunHistory.csv</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Per-run KPIs and processing time, kept beside the audit log for trend charts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>QueueDryRunFile</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Performer in DRYRUN mode: payload file to process. Blank = the newest file in Reports\QueueDryRun.</t>
         </is>
       </c>
     </row>
@@ -1207,6 +1559,7 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1239,6 +1592,8 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>ESCALATE</t>
@@ -1271,6 +1626,8 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1303,6 +1660,8 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1340,6 +1699,7 @@
           <t>GoodsReceived</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1536,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1585,7 +1945,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Transaction identity.</t>
+          <t>Transaction identity. Transforms: NONE, LOWERCASE, UPPERCASE, INTEGER, HEX_TO_INTEGER, DECIMAL, EPOCH_TO_DATETIME, ISO_TO_DATETIME, BOOLEAN, BOOLEAN_INVERT, ABI_STRING, ABI_UINT256, ABI_ADDRESS.</t>
         </is>
       </c>
     </row>
@@ -1605,6 +1965,7 @@
           <t>INTEGER</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1666,6 +2027,7 @@
           <t>LOWERCASE</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1768,12 +2130,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BOOLEAN_INVERT</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Etherscan reports 0 for success.</t>
+          <t>Etherscan reports 1 for a reverted transaction, 0 for success.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RawInput</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Raw call data - hashed into the audit log as InputDataHash.</t>
         </is>
       </c>
     </row>
@@ -1783,6 +2167,262 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BlockchainField</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LogisticsField</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>TransformType</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hash</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TxHash</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ethereum-etl column names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>block_number</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BlockNumber</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>block_timestamp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EventTimestampUtc</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ISO_TO_DATETIME</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>'yyyy-MM-dd HH:mm:ss UTC' rather than epoch seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>from_address</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SenderAddress</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>to_address</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ContractAddress</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>input:selector</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EventSelector</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The export has no methodId column - take the selector from the call data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>input:arg0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ShipmentID</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ABI_STRING</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>input:arg1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OnChainQty</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ABI_UINT256</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>input:arg2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PONumber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ABI_STRING</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>receipt_status</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TxFailed</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BOOLEAN_INVERT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Receipt status 1 means success, so it is inverted into TxFailed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RawInput</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1930,7 +2570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/BlockchainLogisticsValidator/Data/Config.xlsx
+++ b/BlockchainLogisticsValidator/Data/Config.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ValidationRules" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ApprovedWallets" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FieldMapping" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="FieldMapping_EvmEtl" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="EventSequence" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="EventSignatures" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ValidationRules" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ApprovedWallets" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldMapping" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FieldMapping_EvmEtl" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventSequence" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventSignatures" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -548,7 +548,6 @@
           <t>EtherscanApiKey</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Free key from etherscan.io/myapikey. Blank keeps API mode disabled.</t>
@@ -906,7 +905,6 @@
           <t>SmtpUser</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>Leave blank for an unauthenticated relay.</t>
@@ -919,7 +917,6 @@
           <t>SmtpPassword</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>App password. Never commit a real value - use Config.local.json.</t>
@@ -1321,7 +1318,6 @@
           <t>OutlookAccount</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>OUTLOOK mode: send from this account. Blank = the default profile.</t>
@@ -1351,7 +1347,6 @@
           <t>TeamsWebhookUrl</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>Teams Workflows webhook. Blank writes the Adaptive Card payload to Reports instead of posting.</t>
@@ -1364,7 +1359,6 @@
           <t>SlackWebhookUrl</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>Slack incoming webhook. Blank writes the payload to Reports instead of posting.</t>
@@ -1377,7 +1371,6 @@
           <t>DashboardPushUrl</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>Optional: Power BI streaming-dataset push URL or a Google Apps Script web app. Blank = no push.</t>
@@ -1424,7 +1417,6 @@
           <t>QueueDryRunFile</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>Performer in DRYRUN mode: payload file to process. Blank = the newest file in Reports\QueueDryRun.</t>
@@ -1559,7 +1551,6 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1592,8 +1583,6 @@
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>ESCALATE</t>
@@ -1626,8 +1615,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1660,8 +1647,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1699,7 +1684,6 @@
           <t>GoodsReceived</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1965,7 +1949,6 @@
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2027,7 +2010,6 @@
           <t>LOWERCASE</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2241,7 +2223,6 @@
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2281,7 +2262,6 @@
           <t>LOWERCASE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2299,7 +2279,6 @@
           <t>LOWERCASE</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2339,7 +2318,6 @@
           <t>ABI_STRING</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2357,7 +2335,6 @@
           <t>ABI_UINT256</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2375,7 +2352,6 @@
           <t>ABI_STRING</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2415,7 +2391,6 @@
           <t>LOWERCASE</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BlockchainLogisticsValidator/Data/Config.xlsx
+++ b/BlockchainLogisticsValidator/Data/Config.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -548,6 +548,7 @@
           <t>EtherscanApiKey</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Free key from etherscan.io/myapikey. Blank keeps API mode disabled.</t>
@@ -905,6 +906,7 @@
           <t>SmtpUser</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>Leave blank for an unauthenticated relay.</t>
@@ -917,6 +919,7 @@
           <t>SmtpPassword</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>App password. Never commit a real value - use Config.local.json.</t>
@@ -1045,381 +1048,352 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QueueMode</t>
+          <t>RunMode</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DRYRUN</t>
+          <t>BATCH</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ORCHESTRATOR pushes real queue items; DRYRUN writes the payloads to disk for inspection.</t>
+          <t>BATCH validates the whole run in one job; DISPATCH writes a work queue file, one item per shipment, for Workflows\Queue\Performer.xaml to process.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QueueName</t>
+          <t>ExplorerPageUrl</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BlockchainValidationQueue</t>
+          <t>Data\Input\MockChain\explorer_ethereum.html</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Orchestrator queue used by Dispatcher and Performer.</t>
+          <t>Used when DataSourceMode = WEB. A local replica by default; point at a live explorer URL to scrape the real thing.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RunMode</t>
+          <t>ChainRecordsPath</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BATCH</t>
+          <t>result</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BATCH validates the whole run in one job; DISPATCH splits it into one Orchestrator queue item per shipment.</t>
+          <t>JSON path of the transaction array in a MOCK/API response. 'result' for Etherscan.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ExplorerPageUrl</t>
+          <t>FieldMappingSheet</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Data\Input\MockChain\explorer_ethereum.html</t>
+          <t>FieldMapping</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Used when DataSourceMode = WEB. A local replica by default; point at a live explorer URL to scrape the real thing.</t>
+          <t>Which mapping sheet translates the feed's fields. FieldMapping = Etherscan; FieldMapping_EvmEtl = ethereum-etl export.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ChainRecordsPath</t>
+          <t>LogisticsSourceMode</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>EXCEL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JSON path of the transaction array in a MOCK/API response. 'result' for Etherscan.</t>
+          <t>EXCEL | CSV | SQL - where the ERP/WMS records are read from.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FieldMappingSheet</t>
+          <t>ShipmentsCsvFile</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FieldMapping</t>
+          <t>Data\Input\ERP_CSV\Shipments.csv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Which mapping sheet translates the feed's fields. FieldMapping = Etherscan; FieldMapping_EvmEtl = ethereum-etl export.</t>
+          <t>Used when LogisticsSourceMode = CSV.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LogisticsSourceMode</t>
+          <t>ShipmentEventsCsvFile</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EXCEL</t>
+          <t>Data\Input\ERP_CSV\ShipmentEvents.csv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EXCEL | CSV | SQL - where the ERP/WMS records are read from.</t>
+          <t>Used when LogisticsSourceMode = CSV.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ShipmentsCsvFile</t>
+          <t>DbProviderName</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Data\Input\ERP_CSV\Shipments.csv</t>
+          <t>System.Data.Odbc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Used when LogisticsSourceMode = CSV.</t>
+          <t>SQL mode: ADO.NET provider for Database Connect (System.Data.Odbc, System.Data.SqlClient, ...).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ShipmentEventsCsvFile</t>
+          <t>DbConnectionString</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Data\Input\ERP_CSV\ShipmentEvents.csv</t>
+          <t>Driver={Microsoft Access Driver (*.mdb, *.accdb)};Dbq={ProjectRoot}\Data\Input\LogisticsERP.accdb;</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Used when LogisticsSourceMode = CSV.</t>
+          <t>SQL mode. {ProjectRoot} is replaced at run time. Put real credentials in Config.local.json.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DbProviderName</t>
+          <t>DbShipmentsQuery</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>System.Data.Odbc</t>
+          <t>SELECT * FROM Shipments ORDER BY ShipmentID</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SQL mode: ADO.NET provider for Database Connect (System.Data.Odbc, System.Data.SqlClient, ...).</t>
+          <t>SQL mode: must return the Shipments columns.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DbConnectionString</t>
+          <t>DbShipmentEventsQuery</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Driver={Microsoft Access Driver (*.mdb, *.accdb)};Dbq={ProjectRoot}\Data\Input\LogisticsERP.accdb;</t>
+          <t>SELECT * FROM ShipmentEvents ORDER BY ShipmentID, ExpectedEventTimestampUtc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SQL mode. {ProjectRoot} is replaced at run time. Put real credentials in Config.local.json.</t>
+          <t>SQL mode: must return the ShipmentEvents columns.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DbShipmentsQuery</t>
+          <t>ReviewUi</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SELECT * FROM Shipments ORDER BY ShipmentID</t>
+          <t>WINDOW</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SQL mode: must return the Shipments columns.</t>
+          <t>PROMPT mode: WINDOW shows the full review form; DIALOG falls back to a simple Input Dialog.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DbShipmentEventsQuery</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>SELECT * FROM ShipmentEvents ORDER BY ShipmentID, ExpectedEventTimestampUtc</t>
-        </is>
+          <t>ReviewTimeoutMinutes</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>30</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SQL mode: must return the ShipmentEvents columns.</t>
+          <t>An unanswered review window closes after this long and the item is recorded as DEFERRED.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ReviewUi</t>
+          <t>AlertAttachReports</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WINDOW</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PROMPT mode: WINDOW shows the full review form; DIALOG falls back to a simple Input Dialog.</t>
+          <t>Attach the Excel and PDF reports to SMTP / Outlook alerts.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ReviewTimeoutMinutes</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>30</v>
-      </c>
+          <t>OutlookAccount</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>An unanswered review window closes after this long and the item is recorded as DEFERRED.</t>
+          <t>OUTLOOK mode: send from this account. Blank = the default profile.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AlertAttachReports</t>
+          <t>OutlookSaveAsDraft</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Attach the Excel and PDF reports to SMTP / Outlook alerts.</t>
+          <t>OUTLOOK mode: True saves the alert as a draft instead of sending it.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OutlookAccount</t>
-        </is>
-      </c>
+          <t>TeamsWebhookUrl</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OUTLOOK mode: send from this account. Blank = the default profile.</t>
+          <t>Teams Workflows webhook. Blank writes the Adaptive Card payload to Reports instead of posting.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OutlookSaveAsDraft</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
+          <t>SlackWebhookUrl</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OUTLOOK mode: True saves the alert as a draft instead of sending it.</t>
+          <t>Slack incoming webhook. Blank writes the payload to Reports instead of posting.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TeamsWebhookUrl</t>
-        </is>
-      </c>
+          <t>DashboardPushUrl</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Teams Workflows webhook. Blank writes the Adaptive Card payload to Reports instead of posting.</t>
+          <t>Optional: Power BI streaming-dataset push URL or a Google Apps Script web app. Blank = no push.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SlackWebhookUrl</t>
+          <t>DashboardPushFormat</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>POWERBI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Slack incoming webhook. Blank writes the payload to Reports instead of posting.</t>
+          <t>POWERBI posts one flat KPI row; JSON posts the full dashboard_summary.json document.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DashboardPushUrl</t>
+          <t>RunHistoryFile</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RunHistory.csv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Optional: Power BI streaming-dataset push URL or a Google Apps Script web app. Blank = no push.</t>
+          <t>Per-run KPIs and processing time, kept beside the audit log for trend charts.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DashboardPushFormat</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>POWERBI</t>
-        </is>
-      </c>
+          <t>QueueFile</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>POWERBI posts one flat KPI row; JSON posts the full dashboard_summary.json document.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>RunHistoryFile</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>RunHistory.csv</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Per-run KPIs and processing time, kept beside the audit log for trend charts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>QueueDryRunFile</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Performer in DRYRUN mode: payload file to process. Blank = the newest file in Reports\QueueDryRun.</t>
+          <t>Performer: work queue file to process. Blank = the newest file in Reports\WorkQueue.</t>
         </is>
       </c>
     </row>
@@ -1551,6 +1525,7 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1583,6 +1558,8 @@
           <t>CRITICAL</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>ESCALATE</t>
@@ -1615,6 +1592,8 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1647,6 +1626,8 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1684,6 +1665,7 @@
           <t>GoodsReceived</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>FLAG</t>
@@ -1949,6 +1931,7 @@
           <t>INTEGER</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2010,6 +1993,7 @@
           <t>LOWERCASE</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2223,6 +2207,7 @@
           <t>INTEGER</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2262,6 +2247,7 @@
           <t>LOWERCASE</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2279,6 +2265,7 @@
           <t>LOWERCASE</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2318,6 +2305,7 @@
           <t>ABI_STRING</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2335,6 +2323,7 @@
           <t>ABI_UINT256</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2352,6 +2341,7 @@
           <t>ABI_STRING</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2391,6 +2381,7 @@
           <t>LOWERCASE</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
